--- a/grupos/1CV - Estadisticos 20211.xlsx
+++ b/grupos/1CV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="180">
   <si>
     <t>Materia</t>
   </si>
@@ -215,21 +215,21 @@
     <t>Medina Tolentino Francisco</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
     <t>Santiago Hernández Mariana</t>
   </si>
   <si>
-    <t>Villanueva Morales Luis Arturo</t>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -257,136 +257,256 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>QUIÑONES</t>
+  </si>
+  <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>KATHIA</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>FERGIE PAULETTE</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>JAZMIN ADALI</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>FATIMA MARILYN</t>
+  </si>
+  <si>
+    <t>INGRID AMERICA</t>
+  </si>
+  <si>
+    <t>ANGEL URIEL</t>
+  </si>
+  <si>
+    <t>JAIME</t>
+  </si>
+  <si>
+    <t>LUIS REY</t>
+  </si>
+  <si>
+    <t>CITLALI ESPERANZA</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>RUBI</t>
+  </si>
+  <si>
+    <t>MARYFER</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>MERINO</t>
   </si>
   <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
-    <t>MORALES</t>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
   </si>
   <si>
     <t>OLIVARES</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>PALOMARES</t>
   </si>
   <si>
     <t>PELLICO</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>RUGERIO</t>
   </si>
   <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>SOLANO</t>
   </si>
   <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
+    <t>SORIANO</t>
   </si>
   <si>
     <t>VILLA</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>BRETON</t>
   </si>
   <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>CADENA</t>
+  </si>
+  <si>
+    <t>SÁNCHEZ</t>
   </si>
   <si>
     <t>HIPOLITO</t>
   </si>
   <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
     <t>TEQUIHUATLE</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>QUIÑONES</t>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
   </si>
   <si>
     <t>MENA</t>
   </si>
   <si>
-    <t>LEÓN</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>VERA</t>
+    <t>PORRAS</t>
   </si>
   <si>
     <t>MACARIO</t>
   </si>
   <si>
-    <t>KATHIA</t>
-  </si>
-  <si>
-    <t>LUIS ARMANDO</t>
-  </si>
-  <si>
-    <t>FERGIE PAULETTE</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>JAZMIN ADALI</t>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>CRISTAL YOSELIN</t>
+  </si>
+  <si>
+    <t>EVELYN JOHANA</t>
+  </si>
+  <si>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>BERENICE</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
+    <t>VANESSA AMAIRANY</t>
   </si>
   <si>
     <t>REGINA ISABEL</t>
@@ -395,25 +515,25 @@
     <t>VANESSA</t>
   </si>
   <si>
-    <t>FATIMA</t>
+    <t>DIANA IVONNE</t>
+  </si>
+  <si>
+    <t>EVELIN ALEXANDRA</t>
   </si>
   <si>
     <t>ANGELINA</t>
   </si>
   <si>
-    <t>FATIMA MARILYN</t>
+    <t>OLIVA</t>
+  </si>
+  <si>
+    <t>ANA PAOLA</t>
   </si>
   <si>
     <t>JOSE JULIAN</t>
   </si>
   <si>
-    <t>INGRID AMERICA</t>
-  </si>
-  <si>
-    <t>ANGEL URIEL</t>
-  </si>
-  <si>
-    <t>JAIME</t>
+    <t>ITZEL ABIGAIL</t>
   </si>
   <si>
     <t>JAZMIN</t>
@@ -422,142 +542,22 @@
     <t>ALDO GEOVANNI</t>
   </si>
   <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>CITLALI ESPERANZA</t>
+    <t>ALONDRA YURIDIA</t>
   </si>
   <si>
     <t>KIMBERLY</t>
   </si>
   <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
+    <t>ANGEL DAVID</t>
   </si>
   <si>
     <t>ANGELES</t>
   </si>
   <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>MARYFER</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
+    <t>KAREN</t>
   </si>
   <si>
     <t>FLOR GUADALUPE</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>CADENA</t>
-  </si>
-  <si>
-    <t>SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>CRISTAL YOSELIN</t>
-  </si>
-  <si>
-    <t>EVELYN JOHANA</t>
-  </si>
-  <si>
-    <t>YARED</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>BERENICE</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>VANESSA AMAIRANY</t>
-  </si>
-  <si>
-    <t>DIANA IVONNE</t>
-  </si>
-  <si>
-    <t>EVELIN ALEXANDRA</t>
-  </si>
-  <si>
-    <t>OLIVA</t>
-  </si>
-  <si>
-    <t>ANA PAOLA</t>
-  </si>
-  <si>
-    <t>ITZEL ABIGAIL</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>KAREN</t>
   </si>
 </sst>
 </file>
@@ -1061,19 +1061,19 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1100,16 +1100,16 @@
         <v>6</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>9</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -1129,28 +1129,28 @@
         <v>6</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1183,13 +1183,13 @@
         <v>6</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1197,7 +1197,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>-1</v>
@@ -1206,31 +1206,31 @@
         <v>6</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1251,7 +1251,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -1260,13 +1260,13 @@
         <v>6</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1292,22 +1292,22 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1337,10 +1337,10 @@
         <v>6</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>6</v>
@@ -1369,22 +1369,22 @@
         <v>7</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1405,16 +1405,16 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>10</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1446,22 +1446,22 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1485,7 +1485,7 @@
         <v>6</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1494,7 +1494,7 @@
         <v>8</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1520,25 +1520,25 @@
         <v>8</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1568,13 +1568,13 @@
         <v>6</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1600,19 +1600,19 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1636,7 +1636,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>8</v>
@@ -1645,10 +1645,10 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1677,22 +1677,22 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1719,10 +1719,10 @@
         <v>10</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1754,22 +1754,22 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1796,10 +1796,10 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1840,10 +1840,10 @@
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1908,22 +1908,22 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1953,10 +1953,10 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1973,16 +1973,16 @@
         <v>-1</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>8</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1991,13 +1991,13 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -2027,16 +2027,16 @@
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2062,22 +2062,22 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2098,13 +2098,13 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2139,7 +2139,7 @@
         <v>7</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2148,10 +2148,10 @@
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2184,10 +2184,10 @@
         <v>6</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -2201,7 +2201,7 @@
         <v>7</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>6</v>
@@ -2216,19 +2216,19 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2255,16 +2255,16 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>6</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -2278,7 +2278,7 @@
         <v>8</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -2293,22 +2293,22 @@
         <v>8</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2332,7 +2332,7 @@
         <v>8</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2370,22 +2370,22 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2409,10 +2409,10 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2429,7 +2429,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C22">
         <v>-1</v>
@@ -2438,16 +2438,16 @@
         <v>6</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F22">
         <v>7</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2456,10 +2456,10 @@
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2483,7 +2483,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U22">
         <v>-1</v>
@@ -2492,13 +2492,13 @@
         <v>6</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2524,22 +2524,22 @@
         <v>9</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2560,22 +2560,22 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U23">
         <v>10</v>
       </c>
       <c r="V23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X23">
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2586,7 +2586,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D24">
         <v>6</v>
@@ -2598,25 +2598,25 @@
         <v>8</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2640,19 +2640,19 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V24">
         <v>6</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2678,22 +2678,22 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2729,7 +2729,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2764,13 +2764,13 @@
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2806,7 +2806,7 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2814,7 +2814,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C27">
         <v>7</v>
@@ -2823,7 +2823,7 @@
         <v>6</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F27">
         <v>8</v>
@@ -2832,22 +2832,22 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2868,19 +2868,19 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -2909,22 +2909,22 @@
         <v>9</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2948,13 +2948,13 @@
         <v>8</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -2986,22 +2986,22 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3022,13 +3022,13 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -3037,7 +3037,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3060,22 +3060,22 @@
         <v>8</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I30">
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -3105,16 +3105,16 @@
         <v>6</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3131,13 +3131,13 @@
         <v>6</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F31">
         <v>6</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H31">
         <v>-1</v>
@@ -3146,13 +3146,13 @@
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3185,13 +3185,13 @@
         <v>6</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X31">
         <v>6</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3208,13 +3208,13 @@
         <v>-1</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H32">
         <v>-1</v>
@@ -3226,10 +3226,10 @@
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3262,13 +3262,13 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3276,7 +3276,7 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C33">
         <v>-1</v>
@@ -3291,22 +3291,22 @@
         <v>7</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I33">
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3330,22 +3330,22 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U33">
         <v>-1</v>
       </c>
       <c r="V33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3353,7 +3353,7 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C34">
         <v>7</v>
@@ -3362,7 +3362,7 @@
         <v>7</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F34">
         <v>9</v>
@@ -3371,22 +3371,22 @@
         <v>8</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I34">
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3407,7 +3407,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U34">
         <v>7</v>
@@ -3416,13 +3416,13 @@
         <v>7</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X34">
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3445,22 +3445,22 @@
         <v>8</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I35">
         <v>-1</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3499,7 +3499,7 @@
         <v>8</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3525,22 +3525,22 @@
         <v>6</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I36">
         <v>-1</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3573,7 +3573,7 @@
         <v>9</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y36">
         <v>6</v>
@@ -3590,7 +3590,7 @@
         <v>-1</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E37">
         <v>6</v>
@@ -3602,19 +3602,19 @@
         <v>6</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I37">
         <v>-1</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M37">
         <v>-1</v>
@@ -3644,10 +3644,10 @@
         <v>-1</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X37">
         <v>9</v>
@@ -3676,22 +3676,22 @@
         <v>6</v>
       </c>
       <c r="G38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I38">
         <v>-1</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M38">
         <v>-1</v>
@@ -3715,7 +3715,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U38">
         <v>7</v>
@@ -3724,13 +3724,13 @@
         <v>6</v>
       </c>
       <c r="W38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3756,19 +3756,19 @@
         <v>6</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I39">
         <v>-1</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M39">
         <v>-1</v>
@@ -3801,7 +3801,7 @@
         <v>6</v>
       </c>
       <c r="W39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X39">
         <v>8</v>
@@ -3824,7 +3824,7 @@
         <v>-1</v>
       </c>
       <c r="E40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F40">
         <v>10</v>
@@ -3842,10 +3842,10 @@
         <v>-1</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M40">
         <v>-1</v>
@@ -3878,7 +3878,7 @@
         <v>-1</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X40">
         <v>10</v>
@@ -3892,7 +3892,7 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C41">
         <v>10</v>
@@ -3910,22 +3910,22 @@
         <v>8</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I41">
         <v>-1</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3946,16 +3946,16 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U41">
         <v>10</v>
       </c>
       <c r="V41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X41">
         <v>10</v>
@@ -3987,22 +3987,22 @@
         <v>9</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -4023,16 +4023,16 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X42">
         <v>10</v>
@@ -4073,10 +4073,10 @@
         <v>-1</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M43">
         <v>-1</v>
@@ -4109,10 +4109,10 @@
         <v>6</v>
       </c>
       <c r="W43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y43">
         <v>6</v>
@@ -4141,7 +4141,7 @@
         <v>10</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I44">
         <v>-1</v>
@@ -4150,13 +4150,13 @@
         <v>-1</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N44">
         <v>-1</v>
@@ -4192,7 +4192,7 @@
         <v>10</v>
       </c>
       <c r="Y44">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -4215,7 +4215,7 @@
         <v>5</v>
       </c>
       <c r="G45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H45">
         <v>-1</v>
@@ -4227,10 +4227,10 @@
         <v>-1</v>
       </c>
       <c r="K45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M45">
         <v>-1</v>
@@ -4269,7 +4269,7 @@
         <v>5</v>
       </c>
       <c r="Y45">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:25">
@@ -4280,7 +4280,7 @@
         <v>6</v>
       </c>
       <c r="C46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D46">
         <v>6</v>
@@ -4292,25 +4292,25 @@
         <v>7</v>
       </c>
       <c r="G46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I46">
         <v>-1</v>
       </c>
       <c r="J46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N46">
         <v>-1</v>
@@ -4334,19 +4334,19 @@
         <v>6</v>
       </c>
       <c r="U46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V46">
         <v>6</v>
       </c>
       <c r="W46">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X46">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y46">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4411,13 +4411,13 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>53.49</v>
+        <v>62.79</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -4426,15 +4426,15 @@
         <v>8.4</v>
       </c>
       <c r="I2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J2">
-        <v>46.51</v>
+        <v>37.21</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -4443,30 +4443,30 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>67.44</v>
+        <v>83.72</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>32.56</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -4475,30 +4475,30 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>83.72</v>
+      </c>
+      <c r="G4">
+        <v>16.28</v>
+      </c>
+      <c r="H4">
+        <v>6.8</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>69.77</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>7</v>
-      </c>
-      <c r="I4">
-        <v>13</v>
-      </c>
-      <c r="J4">
-        <v>30.23</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
@@ -4507,30 +4507,30 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>81.40000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>18.6</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
@@ -4539,30 +4539,30 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>93.02</v>
+      </c>
+      <c r="G6">
+        <v>6.98</v>
+      </c>
+      <c r="H6">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>86.05</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>6.6</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>13.95</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>69</v>
@@ -4571,25 +4571,25 @@
         <v>43</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>88.37</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4599,7 +4599,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4634,10 +4634,10 @@
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4654,30 +4654,30 @@
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920357</v>
+        <v>21330051920073</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -4688,96 +4688,96 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920357</v>
+        <v>21330051920078</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920357</v>
+        <v>21330051920078</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920073</v>
+        <v>21330051920389</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920073</v>
+        <v>21330051920389</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920073</v>
+        <v>21330051920086</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -4788,196 +4788,196 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920073</v>
+        <v>21330051920089</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920073</v>
+        <v>21330051920089</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920078</v>
+        <v>21330051920089</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920078</v>
+        <v>21330051920094</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920389</v>
+        <v>21330051920094</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920389</v>
+        <v>21330051920095</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920389</v>
+        <v>21330051920095</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920389</v>
+        <v>21330051920095</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920389</v>
+        <v>21330051920096</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920083</v>
+        <v>21330051920099</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="E19" t="s">
         <v>6</v>
@@ -4988,16 +4988,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920084</v>
+        <v>21330051920101</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
@@ -5008,19 +5008,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920086</v>
+        <v>21330051920103</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
         <v>67</v>
@@ -5028,36 +5028,36 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920086</v>
+        <v>21330051920103</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="E22" t="s">
         <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920086</v>
+        <v>21330051920103</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="E23" t="s">
         <v>6</v>
@@ -5068,36 +5068,36 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920086</v>
+        <v>21330051920104</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D24" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920088</v>
+        <v>21330051920107</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="E25" t="s">
         <v>6</v>
@@ -5108,822 +5108,62 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920088</v>
+        <v>21330051920108</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920089</v>
+        <v>21330051920109</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D27" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E27" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920089</v>
+        <v>21330051920109</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E28" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F28" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920089</v>
-      </c>
-      <c r="B29" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" t="s">
-        <v>105</v>
-      </c>
-      <c r="D29" t="s">
-        <v>127</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920092</v>
-      </c>
-      <c r="B30" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" t="s">
-        <v>106</v>
-      </c>
-      <c r="D30" t="s">
-        <v>128</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920092</v>
-      </c>
-      <c r="B31" t="s">
-        <v>84</v>
-      </c>
-      <c r="C31" t="s">
-        <v>106</v>
-      </c>
-      <c r="D31" t="s">
-        <v>128</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920094</v>
-      </c>
-      <c r="B32" t="s">
-        <v>85</v>
-      </c>
-      <c r="C32" t="s">
-        <v>107</v>
-      </c>
-      <c r="D32" t="s">
-        <v>129</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920094</v>
-      </c>
-      <c r="B33" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33" t="s">
-        <v>107</v>
-      </c>
-      <c r="D33" t="s">
-        <v>129</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920094</v>
-      </c>
-      <c r="B34" t="s">
-        <v>85</v>
-      </c>
-      <c r="C34" t="s">
-        <v>107</v>
-      </c>
-      <c r="D34" t="s">
-        <v>129</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920094</v>
-      </c>
-      <c r="B35" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" t="s">
-        <v>107</v>
-      </c>
-      <c r="D35" t="s">
-        <v>129</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920095</v>
-      </c>
-      <c r="B36" t="s">
-        <v>85</v>
-      </c>
-      <c r="C36" t="s">
-        <v>108</v>
-      </c>
-      <c r="D36" t="s">
-        <v>130</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920095</v>
-      </c>
-      <c r="B37" t="s">
-        <v>85</v>
-      </c>
-      <c r="C37" t="s">
-        <v>108</v>
-      </c>
-      <c r="D37" t="s">
-        <v>130</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920095</v>
-      </c>
-      <c r="B38" t="s">
-        <v>85</v>
-      </c>
-      <c r="C38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D38" t="s">
-        <v>130</v>
-      </c>
-      <c r="E38" t="s">
-        <v>5</v>
-      </c>
-      <c r="F38" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920095</v>
-      </c>
-      <c r="B39" t="s">
-        <v>85</v>
-      </c>
-      <c r="C39" t="s">
-        <v>108</v>
-      </c>
-      <c r="D39" t="s">
-        <v>130</v>
-      </c>
-      <c r="E39" t="s">
-        <v>6</v>
-      </c>
-      <c r="F39" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920095</v>
-      </c>
-      <c r="B40" t="s">
-        <v>85</v>
-      </c>
-      <c r="C40" t="s">
-        <v>108</v>
-      </c>
-      <c r="D40" t="s">
-        <v>130</v>
-      </c>
-      <c r="E40" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920095</v>
-      </c>
-      <c r="B41" t="s">
-        <v>85</v>
-      </c>
-      <c r="C41" t="s">
-        <v>108</v>
-      </c>
-      <c r="D41" t="s">
-        <v>130</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920096</v>
-      </c>
-      <c r="B42" t="s">
-        <v>85</v>
-      </c>
-      <c r="C42" t="s">
-        <v>109</v>
-      </c>
-      <c r="D42" t="s">
-        <v>131</v>
-      </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920096</v>
-      </c>
-      <c r="B43" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D43" t="s">
-        <v>131</v>
-      </c>
-      <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920096</v>
-      </c>
-      <c r="B44" t="s">
-        <v>85</v>
-      </c>
-      <c r="C44" t="s">
-        <v>109</v>
-      </c>
-      <c r="D44" t="s">
-        <v>131</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920097</v>
-      </c>
-      <c r="B45" t="s">
-        <v>86</v>
-      </c>
-      <c r="C45" t="s">
-        <v>110</v>
-      </c>
-      <c r="D45" t="s">
-        <v>132</v>
-      </c>
-      <c r="E45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920098</v>
-      </c>
-      <c r="B46" t="s">
-        <v>87</v>
-      </c>
-      <c r="C46" t="s">
-        <v>81</v>
-      </c>
-      <c r="D46" t="s">
-        <v>133</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920098</v>
-      </c>
-      <c r="B47" t="s">
-        <v>87</v>
-      </c>
-      <c r="C47" t="s">
-        <v>81</v>
-      </c>
-      <c r="D47" t="s">
-        <v>133</v>
-      </c>
-      <c r="E47" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920099</v>
-      </c>
-      <c r="B48" t="s">
-        <v>87</v>
-      </c>
-      <c r="C48" t="s">
-        <v>85</v>
-      </c>
-      <c r="D48" t="s">
-        <v>134</v>
-      </c>
-      <c r="E48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920099</v>
-      </c>
-      <c r="B49" t="s">
-        <v>87</v>
-      </c>
-      <c r="C49" t="s">
-        <v>85</v>
-      </c>
-      <c r="D49" t="s">
-        <v>134</v>
-      </c>
-      <c r="E49" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920101</v>
-      </c>
-      <c r="B50" t="s">
-        <v>88</v>
-      </c>
-      <c r="C50" t="s">
-        <v>87</v>
-      </c>
-      <c r="D50" t="s">
-        <v>135</v>
-      </c>
-      <c r="E50" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920101</v>
-      </c>
-      <c r="B51" t="s">
-        <v>88</v>
-      </c>
-      <c r="C51" t="s">
-        <v>87</v>
-      </c>
-      <c r="D51" t="s">
-        <v>135</v>
-      </c>
-      <c r="E51" t="s">
-        <v>6</v>
-      </c>
-      <c r="F51" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920383</v>
-      </c>
-      <c r="B52" t="s">
-        <v>89</v>
-      </c>
-      <c r="C52" t="s">
-        <v>111</v>
-      </c>
-      <c r="D52" t="s">
-        <v>136</v>
-      </c>
-      <c r="E52" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920103</v>
-      </c>
-      <c r="B53" t="s">
-        <v>90</v>
-      </c>
-      <c r="C53" t="s">
-        <v>81</v>
-      </c>
-      <c r="D53" t="s">
-        <v>137</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920103</v>
-      </c>
-      <c r="B54" t="s">
-        <v>90</v>
-      </c>
-      <c r="C54" t="s">
-        <v>81</v>
-      </c>
-      <c r="D54" t="s">
-        <v>137</v>
-      </c>
-      <c r="E54" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920103</v>
-      </c>
-      <c r="B55" t="s">
-        <v>90</v>
-      </c>
-      <c r="C55" t="s">
-        <v>81</v>
-      </c>
-      <c r="D55" t="s">
-        <v>137</v>
-      </c>
-      <c r="E55" t="s">
-        <v>5</v>
-      </c>
-      <c r="F55" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920103</v>
-      </c>
-      <c r="B56" t="s">
-        <v>90</v>
-      </c>
-      <c r="C56" t="s">
-        <v>81</v>
-      </c>
-      <c r="D56" t="s">
-        <v>137</v>
-      </c>
-      <c r="E56" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920104</v>
-      </c>
-      <c r="B57" t="s">
-        <v>91</v>
-      </c>
-      <c r="C57" t="s">
-        <v>112</v>
-      </c>
-      <c r="D57" t="s">
-        <v>138</v>
-      </c>
-      <c r="E57" t="s">
-        <v>6</v>
-      </c>
-      <c r="F57" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920104</v>
-      </c>
-      <c r="B58" t="s">
-        <v>91</v>
-      </c>
-      <c r="C58" t="s">
-        <v>112</v>
-      </c>
-      <c r="D58" t="s">
-        <v>138</v>
-      </c>
-      <c r="E58" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>21330051920105</v>
-      </c>
-      <c r="B59" t="s">
-        <v>92</v>
-      </c>
-      <c r="C59" t="s">
-        <v>113</v>
-      </c>
-      <c r="D59" t="s">
-        <v>139</v>
-      </c>
-      <c r="E59" t="s">
-        <v>5</v>
-      </c>
-      <c r="F59" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>21330051920107</v>
-      </c>
-      <c r="B60" t="s">
-        <v>93</v>
-      </c>
-      <c r="C60" t="s">
-        <v>114</v>
-      </c>
-      <c r="D60" t="s">
-        <v>140</v>
-      </c>
-      <c r="E60" t="s">
-        <v>6</v>
-      </c>
-      <c r="F60" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>21330051920108</v>
-      </c>
-      <c r="B61" t="s">
-        <v>94</v>
-      </c>
-      <c r="C61" t="s">
-        <v>115</v>
-      </c>
-      <c r="D61" t="s">
-        <v>141</v>
-      </c>
-      <c r="E61" t="s">
-        <v>6</v>
-      </c>
-      <c r="F61" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>21330051920109</v>
-      </c>
-      <c r="B62" t="s">
-        <v>94</v>
-      </c>
-      <c r="C62" t="s">
-        <v>116</v>
-      </c>
-      <c r="D62" t="s">
-        <v>142</v>
-      </c>
-      <c r="E62" t="s">
-        <v>5</v>
-      </c>
-      <c r="F62" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>21330051920109</v>
-      </c>
-      <c r="B63" t="s">
-        <v>94</v>
-      </c>
-      <c r="C63" t="s">
-        <v>116</v>
-      </c>
-      <c r="D63" t="s">
-        <v>142</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>21330051920109</v>
-      </c>
-      <c r="B64" t="s">
-        <v>94</v>
-      </c>
-      <c r="C64" t="s">
-        <v>116</v>
-      </c>
-      <c r="D64" t="s">
-        <v>142</v>
-      </c>
-      <c r="E64" t="s">
-        <v>10</v>
-      </c>
-      <c r="F64" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>21330051920387</v>
-      </c>
-      <c r="B65" t="s">
-        <v>95</v>
-      </c>
-      <c r="C65" t="s">
-        <v>117</v>
-      </c>
-      <c r="D65" t="s">
-        <v>143</v>
-      </c>
-      <c r="E65" t="s">
-        <v>6</v>
-      </c>
-      <c r="F65" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>21330051920387</v>
-      </c>
-      <c r="B66" t="s">
-        <v>95</v>
-      </c>
-      <c r="C66" t="s">
-        <v>117</v>
-      </c>
-      <c r="D66" t="s">
-        <v>143</v>
-      </c>
-      <c r="E66" t="s">
-        <v>10</v>
-      </c>
-      <c r="F66" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -5959,87 +5199,87 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920095</v>
+        <v>21330051920089</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" t="s">
         <v>108</v>
       </c>
-      <c r="D2" t="s">
-        <v>130</v>
-      </c>
       <c r="E2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920073</v>
+        <v>21330051920095</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920389</v>
+        <v>21330051920103</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920357</v>
+        <v>21330051920078</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920086</v>
+        <v>21330051920389</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6047,370 +5287,370 @@
         <v>21330051920094</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920103</v>
+        <v>21330051920109</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920089</v>
+        <v>21330051920072</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920096</v>
+        <v>21330051920357</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920109</v>
+        <v>21330051920073</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>142</v>
+        <v>104</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920078</v>
+        <v>21330051920086</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920088</v>
+        <v>21330051920096</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920092</v>
+        <v>21330051920099</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920098</v>
+        <v>21330051920101</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920099</v>
+        <v>21330051920104</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920101</v>
+        <v>21330051920107</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920104</v>
+        <v>21330051920108</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920387</v>
+        <v>21330051920071</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="C19" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D19" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920072</v>
+        <v>21330051920074</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="D20" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920083</v>
+        <v>21330051920075</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="D21" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920084</v>
+        <v>21330051920076</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920097</v>
+        <v>21330051920077</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="D23" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920383</v>
+        <v>21330051920079</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920105</v>
+        <v>21330051920080</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D25" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920107</v>
+        <v>21330051920081</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="D26" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920108</v>
+        <v>21330051920082</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="D27" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920071</v>
+        <v>21330051920083</v>
       </c>
       <c r="B28" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C28" t="s">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="D28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -6418,16 +5658,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920074</v>
+        <v>21330051920084</v>
       </c>
       <c r="B29" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" t="s">
         <v>145</v>
       </c>
-      <c r="C29" t="s">
-        <v>104</v>
-      </c>
       <c r="D29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -6435,16 +5675,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920075</v>
+        <v>21330051920085</v>
       </c>
       <c r="B30" t="s">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>154</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -6452,16 +5692,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920076</v>
+        <v>21330051920087</v>
       </c>
       <c r="B31" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="D31" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -6469,16 +5709,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920077</v>
+        <v>21330051920088</v>
       </c>
       <c r="B32" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C32" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="D32" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -6486,16 +5726,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920079</v>
+        <v>21330051920090</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="C33" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D33" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -6503,16 +5743,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920080</v>
+        <v>21330051920091</v>
       </c>
       <c r="B34" t="s">
+        <v>129</v>
+      </c>
+      <c r="C34" t="s">
         <v>78</v>
       </c>
-      <c r="C34" t="s">
-        <v>79</v>
-      </c>
       <c r="D34" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -6520,13 +5760,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920081</v>
+        <v>21330051920092</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="C35" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D35" t="s">
         <v>170</v>
@@ -6537,13 +5777,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920082</v>
+        <v>21330051920093</v>
       </c>
       <c r="B36" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="C36" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="D36" t="s">
         <v>171</v>
@@ -6554,13 +5794,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920085</v>
+        <v>21330051920097</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="C37" t="s">
-        <v>99</v>
+        <v>149</v>
       </c>
       <c r="D37" t="s">
         <v>172</v>
@@ -6571,13 +5811,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920087</v>
+        <v>21330051920098</v>
       </c>
       <c r="B38" t="s">
-        <v>148</v>
+        <v>82</v>
       </c>
       <c r="C38" t="s">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="D38" t="s">
         <v>173</v>
@@ -6588,13 +5828,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920090</v>
+        <v>21330051920100</v>
       </c>
       <c r="B39" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="C39" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="D39" t="s">
         <v>174</v>
@@ -6605,13 +5845,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>21330051920091</v>
+        <v>21330051920383</v>
       </c>
       <c r="B40" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="C40" t="s">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="D40" t="s">
         <v>175</v>
@@ -6622,13 +5862,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>21330051920093</v>
+        <v>21330051920102</v>
       </c>
       <c r="B41" t="s">
+        <v>135</v>
+      </c>
+      <c r="C41" t="s">
         <v>151</v>
-      </c>
-      <c r="C41" t="s">
-        <v>152</v>
       </c>
       <c r="D41" t="s">
         <v>176</v>
@@ -6639,13 +5879,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>21330051920100</v>
+        <v>21330051920105</v>
       </c>
       <c r="B42" t="s">
+        <v>136</v>
+      </c>
+      <c r="C42" t="s">
         <v>152</v>
-      </c>
-      <c r="C42" t="s">
-        <v>161</v>
       </c>
       <c r="D42" t="s">
         <v>177</v>
@@ -6656,13 +5896,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>21330051920102</v>
+        <v>21330051920106</v>
       </c>
       <c r="B43" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="C43" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D43" t="s">
         <v>178</v>
@@ -6673,13 +5913,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>21330051920106</v>
+        <v>21330051920387</v>
       </c>
       <c r="B44" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="C44" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="D44" t="s">
         <v>179</v>
@@ -6695,7 +5935,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6733,16 +5973,16 @@
         <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -6756,16 +5996,16 @@
         <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -6773,22 +6013,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920088</v>
+        <v>21330051920094</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -6796,22 +6036,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920088</v>
+        <v>21330051920094</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -6819,22 +6059,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920092</v>
+        <v>21330051920096</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -6842,45 +6082,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920092</v>
+        <v>21330051920096</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920098</v>
+        <v>21330051920099</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
         <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -6888,39 +6128,39 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920098</v>
+        <v>21330051920099</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
         <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920099</v>
+        <v>21330051920072</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -6934,22 +6174,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920099</v>
+        <v>21330051920073</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -6957,16 +6197,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920101</v>
+        <v>21330051920086</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -6980,39 +6220,39 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920101</v>
+        <v>21330051920097</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920104</v>
+        <v>21330051920101</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -7029,19 +6269,19 @@
         <v>21330051920104</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G15">
         <v>-1</v>
@@ -7049,16 +6289,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920387</v>
+        <v>21330051920107</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -7072,208 +6312,24 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920387</v>
+        <v>21330051920108</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" t="s">
         <v>117</v>
       </c>
-      <c r="D17" t="s">
-        <v>143</v>
-      </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920072</v>
-      </c>
-      <c r="B18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18" t="s">
-        <v>118</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>64</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920083</v>
-      </c>
-      <c r="B19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" t="s">
-        <v>123</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>64</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920084</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>102</v>
-      </c>
-      <c r="D20" t="s">
-        <v>124</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>64</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920097</v>
-      </c>
-      <c r="B21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" t="s">
-        <v>110</v>
-      </c>
-      <c r="D21" t="s">
-        <v>132</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>65</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920383</v>
-      </c>
-      <c r="B22" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" t="s">
-        <v>111</v>
-      </c>
-      <c r="D22" t="s">
-        <v>136</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>65</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920105</v>
-      </c>
-      <c r="B23" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" t="s">
-        <v>113</v>
-      </c>
-      <c r="D23" t="s">
-        <v>139</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>66</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920107</v>
-      </c>
-      <c r="B24" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" t="s">
-        <v>114</v>
-      </c>
-      <c r="D24" t="s">
-        <v>140</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>64</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920108</v>
-      </c>
-      <c r="B25" t="s">
-        <v>94</v>
-      </c>
-      <c r="C25" t="s">
-        <v>115</v>
-      </c>
-      <c r="D25" t="s">
-        <v>141</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/1CV - Estadisticos 20211.xlsx
+++ b/grupos/1CV - Estadisticos 20211.xlsx
@@ -1757,7 +1757,7 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>8</v>
@@ -1911,7 +1911,7 @@
         <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>8</v>
@@ -3528,7 +3528,7 @@
         <v>6</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J36">
         <v>6</v>
@@ -3564,7 +3564,7 @@
         <v>7</v>
       </c>
       <c r="U36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V36">
         <v>6</v>
@@ -4423,7 +4423,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I2">
         <v>16</v>

--- a/grupos/1CV - Estadisticos 20211.xlsx
+++ b/grupos/1CV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="180">
   <si>
     <t>Materia</t>
   </si>
@@ -77,6 +77,9 @@
     <t>DE LOS SANTOS QUIÑONES GABRIELA</t>
   </si>
   <si>
+    <t>ELPIDIO VAZQUEZ MARYFER</t>
+  </si>
+  <si>
     <t>ESPIRITU ARIAS EVELYN JOHANA</t>
   </si>
   <si>
@@ -176,9 +179,6 @@
     <t>TENTZOHUA LEÓN RUBI</t>
   </si>
   <si>
-    <t>VAZQUEZ LINARES MARYFER</t>
-  </si>
-  <si>
     <t>VAZQUEZ VERA MARIA JOSE</t>
   </si>
   <si>
@@ -215,21 +215,21 @@
     <t>Medina Tolentino Francisco</t>
   </si>
   <si>
+    <t>Santiago Hernández Mariana</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Santiago Hernández Mariana</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -242,6 +242,9 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>CHACÓN</t>
   </si>
   <si>
@@ -251,39 +254,99 @@
     <t>CERON</t>
   </si>
   <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MERINO</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>SANJUAN</t>
   </si>
   <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
     <t>TENTZOHUA</t>
   </si>
   <si>
+    <t>ELPIDIO</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>VILLA</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
@@ -293,18 +356,48 @@
     <t>RUIZ</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
     <t>CARRILLO</t>
   </si>
   <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
+    <t>CADENA</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
     <t>BRAVO</t>
   </si>
   <si>
@@ -314,18 +407,36 @@
     <t>PAZ</t>
   </si>
   <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>QUIÑONES</t>
   </si>
   <si>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
     <t>LEÓN</t>
   </si>
   <si>
-    <t>LINARES</t>
-  </si>
-  <si>
     <t>VERA</t>
   </si>
   <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
     <t>KATHIA</t>
   </si>
   <si>
@@ -335,18 +446,66 @@
     <t>FERGIE PAULETTE</t>
   </si>
   <si>
+    <t>CRISTAL YOSELIN</t>
+  </si>
+  <si>
+    <t>EVELYN JOHANA</t>
+  </si>
+  <si>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
     <t>MIROSLAVA</t>
   </si>
   <si>
+    <t>BERENICE</t>
+  </si>
+  <si>
     <t>JAZMIN ADALI</t>
   </si>
   <si>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
+    <t>VANESSA AMAIRANY</t>
+  </si>
+  <si>
+    <t>REGINA ISABEL</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>DIANA IVONNE</t>
+  </si>
+  <si>
     <t>FATIMA</t>
   </si>
   <si>
+    <t>EVELIN ALEXANDRA</t>
+  </si>
+  <si>
+    <t>ANGELINA</t>
+  </si>
+  <si>
     <t>FATIMA MARILYN</t>
   </si>
   <si>
+    <t>OLIVA</t>
+  </si>
+  <si>
+    <t>ANA PAOLA</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>ITZEL ABIGAIL</t>
+  </si>
+  <si>
     <t>INGRID AMERICA</t>
   </si>
   <si>
@@ -356,18 +515,39 @@
     <t>JAIME</t>
   </si>
   <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>ALDO GEOVANNI</t>
+  </si>
+  <si>
     <t>LUIS REY</t>
   </si>
   <si>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
     <t>CITLALI ESPERANZA</t>
   </si>
   <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
     <t>ALMA KAREN</t>
   </si>
   <si>
     <t>GABRIELA</t>
   </si>
   <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
     <t>RUBI</t>
   </si>
   <si>
@@ -375,186 +555,6 @@
   </si>
   <si>
     <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>CADENA</t>
-  </si>
-  <si>
-    <t>SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MENA</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>CRISTAL YOSELIN</t>
-  </si>
-  <si>
-    <t>EVELYN JOHANA</t>
-  </si>
-  <si>
-    <t>YARED</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>BERENICE</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>VANESSA AMAIRANY</t>
-  </si>
-  <si>
-    <t>REGINA ISABEL</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>DIANA IVONNE</t>
-  </si>
-  <si>
-    <t>EVELIN ALEXANDRA</t>
-  </si>
-  <si>
-    <t>ANGELINA</t>
-  </si>
-  <si>
-    <t>OLIVA</t>
-  </si>
-  <si>
-    <t>ANA PAOLA</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>ITZEL ABIGAIL</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>ALDO GEOVANNI</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>KAREN</t>
   </si>
   <si>
     <t>FLOR GUADALUPE</t>
@@ -1076,25 +1076,25 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>6</v>
@@ -1103,7 +1103,7 @@
         <v>9</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -1112,7 +1112,7 @@
         <v>10</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1123,7 +1123,7 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -1141,7 +1141,7 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1153,31 +1153,31 @@
         <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
         <v>6</v>
@@ -1186,7 +1186,7 @@
         <v>6</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1200,7 +1200,7 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D6">
         <v>6</v>
@@ -1218,7 +1218,7 @@
         <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1233,28 +1233,28 @@
         <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>6</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>6</v>
@@ -1266,7 +1266,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1277,7 +1277,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1295,7 +1295,7 @@
         <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1310,34 +1310,34 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>6</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -1387,28 +1387,28 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
         <v>7</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>7</v>
@@ -1464,31 +1464,31 @@
         <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>6</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1508,7 +1508,7 @@
         <v>6</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>6</v>
@@ -1526,7 +1526,7 @@
         <v>6</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1541,28 +1541,28 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>6</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>6</v>
@@ -1574,7 +1574,7 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1582,70 +1582,70 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H11">
         <v>7</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>7</v>
       </c>
       <c r="L11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1659,64 +1659,64 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H12">
         <v>7</v>
       </c>
       <c r="I12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>7</v>
       </c>
       <c r="K12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L12">
         <v>10</v>
       </c>
       <c r="M12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>7</v>
@@ -1728,7 +1728,7 @@
         <v>10</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1736,73 +1736,73 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>9</v>
       </c>
       <c r="L13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1813,76 +1813,76 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1890,76 +1890,76 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F15">
         <v>8</v>
       </c>
       <c r="G15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1967,76 +1967,76 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X16">
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2044,76 +2044,76 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I17">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2124,73 +2124,73 @@
         <v>8</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18">
         <v>9</v>
       </c>
       <c r="F18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2198,10 +2198,10 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D19">
         <v>6</v>
@@ -2210,13 +2210,13 @@
         <v>9</v>
       </c>
       <c r="F19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>8</v>
@@ -2231,31 +2231,31 @@
         <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>7</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>6</v>
@@ -2264,7 +2264,7 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -2275,76 +2275,76 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20">
         <v>9</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>7</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2352,13 +2352,13 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21">
         <v>9</v>
@@ -2367,16 +2367,16 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K21">
         <v>9</v>
@@ -2385,31 +2385,31 @@
         <v>10</v>
       </c>
       <c r="M21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -2421,7 +2421,7 @@
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2429,76 +2429,76 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D22">
         <v>6</v>
       </c>
       <c r="E22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2506,76 +2506,76 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D23">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E23">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I23">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M23">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2583,76 +2583,76 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K24">
         <v>10</v>
       </c>
       <c r="L24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2660,76 +2660,76 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G25">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H25">
         <v>6</v>
       </c>
       <c r="I25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K25">
         <v>10</v>
       </c>
       <c r="L25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2737,76 +2737,76 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M26">
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2817,13 +2817,13 @@
         <v>6</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F27">
         <v>8</v>
@@ -2835,55 +2835,55 @@
         <v>6</v>
       </c>
       <c r="I27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J27">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
         <v>6</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2891,25 +2891,25 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C28">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D28">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E28">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I28">
         <v>10</v>
@@ -2918,49 +2918,49 @@
         <v>9</v>
       </c>
       <c r="K28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2971,73 +2971,73 @@
         <v>8</v>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E29">
         <v>9</v>
       </c>
       <c r="F29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I29">
         <v>10</v>
       </c>
       <c r="J29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3045,76 +3045,76 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E30">
         <v>9</v>
       </c>
       <c r="F30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H30">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
         <v>8</v>
       </c>
       <c r="K30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L30">
         <v>9</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U30">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3122,76 +3122,76 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D31">
         <v>6</v>
       </c>
       <c r="E31">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V31">
         <v>6</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3199,73 +3199,73 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E32">
         <v>6</v>
       </c>
       <c r="F32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
         <v>6</v>
       </c>
       <c r="L32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>6</v>
       </c>
       <c r="X32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y32">
         <v>5</v>
@@ -3279,16 +3279,16 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33">
         <v>6</v>
       </c>
       <c r="F33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -3297,52 +3297,52 @@
         <v>6</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L33">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
         <v>6</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y33">
         <v>5</v>
@@ -3356,31 +3356,31 @@
         <v>6</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F34">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G34">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H34">
         <v>6</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>8</v>
@@ -3389,40 +3389,40 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
         <v>6</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3433,73 +3433,73 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D35">
         <v>7</v>
       </c>
       <c r="E35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G35">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H35">
         <v>6</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J35">
         <v>6</v>
       </c>
       <c r="K35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L35">
         <v>8</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>6</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3507,73 +3507,73 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H36">
         <v>6</v>
       </c>
       <c r="I36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J36">
         <v>6</v>
       </c>
       <c r="K36">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M36">
         <v>6</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U36">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V36">
         <v>6</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y36">
         <v>6</v>
@@ -3584,16 +3584,16 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D37">
         <v>6</v>
       </c>
       <c r="E37">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F37">
         <v>9</v>
@@ -3605,55 +3605,55 @@
         <v>6</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3661,31 +3661,31 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D38">
         <v>6</v>
       </c>
       <c r="E38">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F38">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G38">
         <v>6</v>
       </c>
       <c r="H38">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K38">
         <v>10</v>
@@ -3694,40 +3694,40 @@
         <v>9</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T38">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y38">
         <v>6</v>
@@ -3738,10 +3738,10 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C39">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D39">
         <v>6</v>
@@ -3750,16 +3750,16 @@
         <v>9</v>
       </c>
       <c r="F39">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G39">
         <v>6</v>
       </c>
       <c r="H39">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J39">
         <v>6</v>
@@ -3768,34 +3768,34 @@
         <v>10</v>
       </c>
       <c r="L39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T39">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U39">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V39">
         <v>6</v>
@@ -3815,76 +3815,76 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E40">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K40">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W40">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y40">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3895,73 +3895,73 @@
         <v>6</v>
       </c>
       <c r="C41">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D41">
         <v>6</v>
       </c>
       <c r="E41">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F41">
         <v>10</v>
       </c>
       <c r="G41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H41">
         <v>6</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K41">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T41">
         <v>6</v>
       </c>
       <c r="U41">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W41">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X41">
         <v>10</v>
       </c>
       <c r="Y41">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3969,13 +3969,13 @@
         <v>50</v>
       </c>
       <c r="B42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D42">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E42">
         <v>8</v>
@@ -3984,61 +3984,61 @@
         <v>10</v>
       </c>
       <c r="G42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H42">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J42">
         <v>7</v>
       </c>
       <c r="K42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L42">
         <v>10</v>
       </c>
       <c r="M42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T42">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V42">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X42">
         <v>10</v>
       </c>
       <c r="Y42">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -4046,76 +4046,76 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D43">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E43">
         <v>8</v>
       </c>
       <c r="F43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G43">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K43">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L43">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T43">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V43">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W43">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X43">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y43">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -4123,10 +4123,10 @@
         <v>52</v>
       </c>
       <c r="B44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D44">
         <v>6</v>
@@ -4135,64 +4135,64 @@
         <v>8</v>
       </c>
       <c r="F44">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G44">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L44">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M44">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V44">
         <v>6</v>
       </c>
       <c r="W44">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X44">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y44">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -4200,10 +4200,10 @@
         <v>53</v>
       </c>
       <c r="B45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D45">
         <v>6</v>
@@ -4218,13 +4218,13 @@
         <v>5</v>
       </c>
       <c r="H45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K45">
         <v>8</v>
@@ -4233,40 +4233,40 @@
         <v>5</v>
       </c>
       <c r="M45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W45">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y45">
         <v>5</v>
@@ -4298,7 +4298,7 @@
         <v>6</v>
       </c>
       <c r="I46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J46">
         <v>6</v>
@@ -4313,40 +4313,40 @@
         <v>6</v>
       </c>
       <c r="N46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V46">
         <v>6</v>
       </c>
       <c r="W46">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X46">
         <v>8</v>
       </c>
       <c r="Y46">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4411,30 +4411,30 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>62.79</v>
+        <v>69.77</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>30.23</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="I2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>37.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -4443,30 +4443,30 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>83.72</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>18.6</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>16.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -4475,19 +4475,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>83.72</v>
+        <v>88.37</v>
       </c>
       <c r="G4">
-        <v>16.28</v>
+        <v>11.63</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4498,7 +4498,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
@@ -4507,30 +4507,30 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>90.7</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
@@ -4539,19 +4539,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>93.02</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>6.98</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4562,7 +4562,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>69</v>
@@ -4583,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4599,7 +4599,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4624,546 +4624,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920072</v>
-      </c>
-      <c r="B2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920357</v>
-      </c>
-      <c r="B3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920073</v>
-      </c>
-      <c r="B4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920078</v>
-      </c>
-      <c r="B5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D5" t="s">
-        <v>105</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920078</v>
-      </c>
-      <c r="B6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920389</v>
-      </c>
-      <c r="B7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920389</v>
-      </c>
-      <c r="B8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" t="s">
-        <v>106</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920086</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" t="s">
-        <v>107</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920089</v>
-      </c>
-      <c r="B10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920089</v>
-      </c>
-      <c r="B11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" t="s">
-        <v>108</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920089</v>
-      </c>
-      <c r="B12" t="s">
-        <v>80</v>
-      </c>
-      <c r="C12" t="s">
-        <v>94</v>
-      </c>
-      <c r="D12" t="s">
-        <v>108</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920094</v>
-      </c>
-      <c r="B13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13" t="s">
-        <v>109</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920094</v>
-      </c>
-      <c r="B14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" t="s">
-        <v>109</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920095</v>
-      </c>
-      <c r="B15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920095</v>
-      </c>
-      <c r="B16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" t="s">
-        <v>110</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920095</v>
-      </c>
-      <c r="B17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" t="s">
-        <v>110</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920096</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" t="s">
-        <v>111</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920099</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" t="s">
-        <v>112</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920101</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" t="s">
-        <v>113</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920103</v>
-      </c>
-      <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" t="s">
-        <v>79</v>
-      </c>
-      <c r="D21" t="s">
-        <v>114</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920103</v>
-      </c>
-      <c r="B22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" t="s">
-        <v>114</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920103</v>
-      </c>
-      <c r="B23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23" t="s">
-        <v>114</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920104</v>
-      </c>
-      <c r="B24" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" t="s">
-        <v>115</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920107</v>
-      </c>
-      <c r="B25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" t="s">
-        <v>99</v>
-      </c>
-      <c r="D25" t="s">
-        <v>116</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920108</v>
-      </c>
-      <c r="B26" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" t="s">
-        <v>117</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920109</v>
-      </c>
-      <c r="B27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" t="s">
-        <v>101</v>
-      </c>
-      <c r="D27" t="s">
-        <v>118</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920109</v>
-      </c>
-      <c r="B28" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" t="s">
-        <v>101</v>
-      </c>
-      <c r="D28" t="s">
-        <v>118</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -5199,305 +4659,305 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920089</v>
+        <v>21330051920071</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920095</v>
+        <v>21330051920072</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920103</v>
+        <v>21330051920357</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920078</v>
+        <v>21330051920073</v>
       </c>
       <c r="B5" t="s">
         <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920389</v>
+        <v>21330051920074</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920094</v>
+        <v>21330051920075</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920109</v>
+        <v>21330051920076</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920072</v>
+        <v>21330051920077</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920357</v>
+        <v>21330051920078</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920073</v>
+        <v>21330051920079</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920086</v>
+        <v>21330051920389</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920096</v>
+        <v>21330051920080</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920099</v>
+        <v>21330051920081</v>
       </c>
       <c r="B14" t="s">
         <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920101</v>
+        <v>21330051920082</v>
       </c>
       <c r="B15" t="s">
         <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920104</v>
+        <v>21330051920083</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920107</v>
+        <v>21330051920084</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="D17" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920108</v>
+        <v>21330051920085</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="D18" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920071</v>
+        <v>21330051920086</v>
       </c>
       <c r="B19" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -5505,16 +4965,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920074</v>
+        <v>21330051920087</v>
       </c>
       <c r="B20" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="D20" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5522,16 +4982,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920075</v>
+        <v>21330051920088</v>
       </c>
       <c r="B21" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -5539,16 +4999,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920076</v>
+        <v>21330051920089</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="D22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -5556,16 +5016,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920077</v>
+        <v>21330051920090</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="D23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -5573,16 +5033,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920079</v>
+        <v>21330051920091</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="D24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -5590,16 +5050,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920080</v>
+        <v>21330051920092</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -5607,13 +5067,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920081</v>
+        <v>21330051920093</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>143</v>
+        <v>97</v>
       </c>
       <c r="D26" t="s">
         <v>161</v>
@@ -5624,13 +5084,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920082</v>
+        <v>21330051920094</v>
       </c>
       <c r="B27" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s">
         <v>162</v>
@@ -5641,13 +5101,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920083</v>
+        <v>21330051920095</v>
       </c>
       <c r="B28" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
         <v>163</v>
@@ -5658,13 +5118,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920084</v>
+        <v>21330051920096</v>
       </c>
       <c r="B29" t="s">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="D29" t="s">
         <v>164</v>
@@ -5675,13 +5135,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920085</v>
+        <v>21330051920097</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="D30" t="s">
         <v>165</v>
@@ -5692,13 +5152,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920087</v>
+        <v>21330051920098</v>
       </c>
       <c r="B31" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
       <c r="D31" t="s">
         <v>166</v>
@@ -5709,13 +5169,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920088</v>
+        <v>21330051920099</v>
       </c>
       <c r="B32" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>139</v>
+        <v>94</v>
       </c>
       <c r="D32" t="s">
         <v>167</v>
@@ -5726,13 +5186,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920090</v>
+        <v>21330051920100</v>
       </c>
       <c r="B33" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="D33" t="s">
         <v>168</v>
@@ -5743,13 +5203,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920091</v>
+        <v>21330051920101</v>
       </c>
       <c r="B34" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="D34" t="s">
         <v>169</v>
@@ -5760,13 +5220,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920092</v>
+        <v>21330051920383</v>
       </c>
       <c r="B35" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="D35" t="s">
         <v>170</v>
@@ -5777,13 +5237,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920093</v>
+        <v>21330051920102</v>
       </c>
       <c r="B36" t="s">
+        <v>100</v>
+      </c>
+      <c r="C36" t="s">
         <v>131</v>
-      </c>
-      <c r="C36" t="s">
-        <v>133</v>
       </c>
       <c r="D36" t="s">
         <v>171</v>
@@ -5794,13 +5254,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920097</v>
+        <v>21330051920103</v>
       </c>
       <c r="B37" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>149</v>
+        <v>86</v>
       </c>
       <c r="D37" t="s">
         <v>172</v>
@@ -5811,13 +5271,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920098</v>
+        <v>21330051920104</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="C38" t="s">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="D38" t="s">
         <v>173</v>
@@ -5828,13 +5288,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920100</v>
+        <v>21330051920105</v>
       </c>
       <c r="B39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39" t="s">
         <v>133</v>
-      </c>
-      <c r="C39" t="s">
-        <v>150</v>
       </c>
       <c r="D39" t="s">
         <v>174</v>
@@ -5845,13 +5305,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>21330051920383</v>
+        <v>21330051920106</v>
       </c>
       <c r="B40" t="s">
+        <v>104</v>
+      </c>
+      <c r="C40" t="s">
         <v>134</v>
-      </c>
-      <c r="C40" t="s">
-        <v>135</v>
       </c>
       <c r="D40" t="s">
         <v>175</v>
@@ -5862,13 +5322,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>21330051920102</v>
+        <v>21330051920107</v>
       </c>
       <c r="B41" t="s">
+        <v>105</v>
+      </c>
+      <c r="C41" t="s">
         <v>135</v>
-      </c>
-      <c r="C41" t="s">
-        <v>151</v>
       </c>
       <c r="D41" t="s">
         <v>176</v>
@@ -5879,13 +5339,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>21330051920105</v>
+        <v>21330051920108</v>
       </c>
       <c r="B42" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="C42" t="s">
-        <v>152</v>
+        <v>107</v>
       </c>
       <c r="D42" t="s">
         <v>177</v>
@@ -5896,13 +5356,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>21330051920106</v>
+        <v>21330051920109</v>
       </c>
       <c r="B43" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="C43" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="D43" t="s">
         <v>178</v>
@@ -5916,10 +5376,10 @@
         <v>21330051920387</v>
       </c>
       <c r="B44" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="C44" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="D44" t="s">
         <v>179</v>
@@ -5935,7 +5395,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5967,108 +5427,108 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920078</v>
+        <v>21330051920357</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920078</v>
+        <v>21330051920357</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920094</v>
+        <v>21330051920389</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920094</v>
+        <v>21330051920389</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920096</v>
+        <v>21330051920094</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -6077,27 +5537,27 @@
         <v>64</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920096</v>
+        <v>21330051920094</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6105,16 +5565,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920099</v>
+        <v>21330051920097</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>165</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -6123,27 +5583,27 @@
         <v>64</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920099</v>
+        <v>21330051920097</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>165</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6151,16 +5611,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920072</v>
+        <v>21330051920107</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -6169,44 +5629,44 @@
         <v>64</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920073</v>
+        <v>21330051920107</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920086</v>
+        <v>21330051920108</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>177</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -6215,24 +5675,24 @@
         <v>64</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920097</v>
+        <v>21330051920108</v>
       </c>
       <c r="B13" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="C13" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
         <v>66</v>
@@ -6243,62 +5703,62 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920101</v>
+        <v>21330051920073</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920104</v>
+        <v>21330051920078</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920107</v>
+        <v>21330051920086</v>
       </c>
       <c r="B16" t="s">
         <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -6307,21 +5767,21 @@
         <v>64</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920108</v>
+        <v>21330051920088</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
@@ -6330,7 +5790,99 @@
         <v>64</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>21330051920089</v>
+      </c>
+      <c r="B18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>66</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920098</v>
+      </c>
+      <c r="B19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" t="s">
+        <v>166</v>
+      </c>
+      <c r="E19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>64</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920383</v>
+      </c>
+      <c r="B20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" t="s">
+        <v>170</v>
+      </c>
+      <c r="E20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920103</v>
+      </c>
+      <c r="B21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" t="s">
+        <v>172</v>
+      </c>
+      <c r="E21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" t="s">
+        <v>64</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
